--- a/lab3/tests.xlsx
+++ b/lab3/tests.xlsx
@@ -1,28 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sofan\Desktop\ycheba\ооп\OOP_lab\lab3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{885E5D9B-5FE3-4736-BEBB-9F83E4C121B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC90DAFA-BD59-4764-88BA-856CFCAA8154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Л3_Тесты" sheetId="1" r:id="rId1"/>
-    <sheet name="Л3_ЧЯ" sheetId="2" r:id="rId2"/>
-    <sheet name="Л3_БЯ" sheetId="3" r:id="rId3"/>
+    <sheet name="Л3_БЯ" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="70">
   <si>
     <t>№ теста</t>
   </si>
@@ -150,9 +149,6 @@
     <t>правая граница диапазона (x=b)</t>
   </si>
   <si>
-    <t>классы входных данных</t>
-  </si>
-  <si>
     <t>Т1</t>
   </si>
   <si>
@@ -183,33 +179,6 @@
     <t>Т10</t>
   </si>
   <si>
-    <t>x = a = 0.1 (левая граница диапазона)</t>
-  </si>
-  <si>
-    <t>0.1 &lt; x &lt; 0.5 (малые x, быстрая сходимость)</t>
-  </si>
-  <si>
-    <t>0.5 ≤ x &lt; 1 (средние и большие x)</t>
-  </si>
-  <si>
-    <t>x = b = 1 (правая граница диапазона)</t>
-  </si>
-  <si>
-    <t>корректные данные: x ∈ [0.1; 1], шаг h = 0.1</t>
-  </si>
-  <si>
-    <t>классы выходных данных</t>
-  </si>
-  <si>
-    <t>Y — точное значение функции (1+2x²)·e^(x²)</t>
-  </si>
-  <si>
-    <t>SE состоит из 3–5 слагаемых (малые x)</t>
-  </si>
-  <si>
-    <t>SE состоит из 6–9 слагаемых (большие x)</t>
-  </si>
-  <si>
     <t>Операторы</t>
   </si>
   <si>
@@ -259,12 +228,6 @@
   </si>
   <si>
     <t>y = (1+2x²)·Math.Exp(x²); вывод</t>
-  </si>
-  <si>
-    <t>SN</t>
-  </si>
-  <si>
-    <t>SE</t>
   </si>
   <si>
     <t>x = a + i·h; first_sg = 1; sn = 0</t>
@@ -351,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -370,7 +333,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -872,10 +834,6 @@
     </row>
     <row r="13" spans="1:5" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -883,340 +841,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="11" width="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1228,46 +852,46 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>8</v>
@@ -1303,7 +927,7 @@
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1320,10 +944,10 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>8</v>
@@ -1358,10 +982,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>8</v>
@@ -1397,7 +1021,7 @@
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="3" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>8</v>
@@ -1432,10 +1056,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>8</v>
@@ -1470,10 +1094,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>8</v>
@@ -1509,7 +1133,7 @@
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="3" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>8</v>
@@ -1544,10 +1168,10 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>8</v>
@@ -1567,7 +1191,7 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="3" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -1591,7 +1215,7 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -1614,10 +1238,10 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>8</v>
